--- a/astro-site/public/dl/taco-shop-checklist-templates/06-taco-shop-duties-by-role.xlsx
+++ b/astro-site/public/dl/taco-shop-checklist-templates/06-taco-shop-duties-by-role.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>9:30 AM</t>
         </is>
       </c>
       <c r="F6" s="13" t="n"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>9:45 AM</t>
         </is>
       </c>
       <c r="F7" s="13" t="n"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>10:20 AM</t>
         </is>
       </c>
       <c r="F8" s="13" t="n"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>1:15 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="F9" s="13" t="n"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Clean, then sanitize the tortilleria corn mill (corn tortilla production area) before grinding (sanitizer at label concentration, checked with a test strip)</t>
+          <t>Clean, then sanitize the corn mill before grinding (sanitizer at label concentration, checked with a test strip)</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Assign the salsa prep cook (in charge of salsas) the grinding and labeling of the day's salsas</t>
+          <t>Take charge of the day's salsas: grinding and labeling each one</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Check the oil's smoke point before service and note any issue</t>
+          <t>Check the fryer oil's condition (color, odor, foaming) before service and note any issue</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Ask about allergies and intolerances before closing out each ticket</t>
+          <t>Ask about allergies and intolerances when taking each order</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Measure the hot order's temperature before handing it to the delivery driver: hot at 135 °F or above in the insulated delivery bag, cold items apart at 41 °F or below — log reading: ____ °F</t>
+          <t>Check the hot order is at 135 °F or above at pickup, before you leave (cold items apart at 41 °F or below) — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
